--- a/InputData/Clean/EnvironmentalData/DLI-All.xlsx
+++ b/InputData/Clean/EnvironmentalData/DLI-All.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd HH:mm:ss UTC"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D189"/>
+  <dimension ref="A1:D204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -3391,6 +3391,246 @@
         <v>0.054461384305</v>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" s="2">
+        <v>45455</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>948</v>
+      </c>
+      <c r="D190">
+        <v>3.4128</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2">
+        <v>45565</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>816</v>
+      </c>
+      <c r="D191">
+        <v>2.9376</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2">
+        <v>45572</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>804</v>
+      </c>
+      <c r="D192">
+        <v>2.8944</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2">
+        <v>45579</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>240</v>
+      </c>
+      <c r="D193">
+        <v>0.864</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2">
+        <v>45600</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>684</v>
+      </c>
+      <c r="D194">
+        <v>2.4624</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2">
+        <v>45607</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>840</v>
+      </c>
+      <c r="D195">
+        <v>3.024</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2">
+        <v>45614</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>492</v>
+      </c>
+      <c r="D196">
+        <v>1.7712</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2">
+        <v>45621</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>468</v>
+      </c>
+      <c r="D197">
+        <v>1.6848</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2">
+        <v>45628</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>756</v>
+      </c>
+      <c r="D198">
+        <v>2.7216</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2">
+        <v>45639</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>576</v>
+      </c>
+      <c r="D199">
+        <v>2.0736</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2">
+        <v>45691</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>840</v>
+      </c>
+      <c r="D200">
+        <v>3.024</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2">
+        <v>45705</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>744</v>
+      </c>
+      <c r="D201">
+        <v>2.6784</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2">
+        <v>45712</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>792</v>
+      </c>
+      <c r="D202">
+        <v>2.8512</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2">
+        <v>45719</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>756</v>
+      </c>
+      <c r="D203">
+        <v>2.7216</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2">
+        <v>45733</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>912</v>
+      </c>
+      <c r="D204">
+        <v>3.2832</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
